--- a/documents/00. Database-ERD-Schemas.xlsx
+++ b/documents/00. Database-ERD-Schemas.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrosea-my.sharepoint.com/personal/harry_kurniansyah_petrosea_com/Documents/Documents/2_Harry_Kurniansyah_Docs/0_Very_Personal/MechSense/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{129A03A8-A3D7-4999-8567-DA1EBD7805CC}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BAF7C0-F6EF-40DF-9203-B60BC497B66A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ERD" sheetId="1" r:id="rId1"/>
     <sheet name="Table - Site Master" sheetId="2" r:id="rId2"/>
+    <sheet name="Table - Brand Master" sheetId="3" r:id="rId3"/>
+    <sheet name="Table - Equipment Class Master" sheetId="4" r:id="rId4"/>
+    <sheet name="Table -Model Master" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,54 +29,221 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>site_code</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>location</t>
-  </si>
-  <si>
-    <t>longitude</t>
-  </si>
-  <si>
-    <t>latitude</t>
-  </si>
-  <si>
-    <t>establishment_year</t>
-  </si>
-  <si>
-    <t>project_code</t>
-  </si>
-  <si>
-    <t>end_target_year</t>
-  </si>
-  <si>
-    <t>is_active</t>
-  </si>
-  <si>
-    <t>created_by</t>
-  </si>
-  <si>
-    <t>created_date</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>deleted_at</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="61">
+  <si>
+    <t>{uuid}</t>
+  </si>
+  <si>
+    <t>KJA</t>
+  </si>
+  <si>
+    <t>KIDECO JAYA AGUNG</t>
+  </si>
+  <si>
+    <t>55M5+2H2, Rangan, Kuaro, Paser Regency, East Kalimantan 76281</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>KOM</t>
+  </si>
+  <si>
+    <t>LBR</t>
+  </si>
+  <si>
+    <t>SNY</t>
+  </si>
+  <si>
+    <t>CATERPILLAR</t>
+  </si>
+  <si>
+    <t>KOMATSU</t>
+  </si>
+  <si>
+    <t>LIEBHERR</t>
+  </si>
+  <si>
+    <t>SANY</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>HYUNDAI</t>
+  </si>
+  <si>
+    <t>OHT</t>
+  </si>
+  <si>
+    <t>EXC</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>Off Highway Truck</t>
+  </si>
+  <si>
+    <t>Excavator</t>
+  </si>
+  <si>
+    <t>Dozer</t>
+  </si>
+  <si>
+    <t>Payload Capacity</t>
+  </si>
+  <si>
+    <t>Bucket Volume</t>
+  </si>
+  <si>
+    <t>Blade Width</t>
+  </si>
+  <si>
+    <t>Ton</t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t>Feet</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>Grader</t>
+  </si>
+  <si>
+    <t>Driller</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>Diameter Lubang Bor</t>
+  </si>
+  <si>
+    <t>777D</t>
+  </si>
+  <si>
+    <t>HD785-7</t>
+  </si>
+  <si>
+    <t>PC3400-11</t>
+  </si>
+  <si>
+    <t>{uuid-fk1}</t>
+  </si>
+  <si>
+    <t>{uuid-fk2}</t>
+  </si>
+  <si>
+    <t>project_code
+(INTEGER)</t>
+  </si>
+  <si>
+    <t>site_code
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>name
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>location
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>long_lat
+(POINTS)</t>
+  </si>
+  <si>
+    <t>(-1.81400199008506, 116.15949417064)</t>
+  </si>
+  <si>
+    <t>establishment_year
+(INTEGER)</t>
+  </si>
+  <si>
+    <t>end_target_year
+(INTEGER)</t>
+  </si>
+  <si>
+    <t>is_active
+(BOOLEAN)</t>
+  </si>
+  <si>
+    <t>created_by
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>created_at
+(TIMESTAMP)</t>
+  </si>
+  <si>
+    <t>updated_at
+(TIMESTAMP)</t>
+  </si>
+  <si>
+    <t>deleted_at
+(TIMESTAMP)</t>
+  </si>
+  <si>
+    <t>id
+(UUID)</t>
+  </si>
+  <si>
+    <t>brand_code
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>brand_name
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>class_code
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>description
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>primary_metric
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>metric_unit
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>standard_metric_value
+(NUMERIC (10,2))</t>
+  </si>
+  <si>
+    <t>model_name
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>class_id
+(UUID)</t>
+  </si>
+  <si>
+    <t>brand_id
+(UUID)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -103,8 +273,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,60 +568,617 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C4114C-3269-42E0-A2EE-B55B0E7032E4}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1234</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>2026</v>
+      </c>
+      <c r="H2">
+        <v>2036</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F10698-B894-4157-9D90-FB68318B125C}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="G3" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="G5" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="G6" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B34790-3214-40B1-A3B8-A15FC42E8D0D}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I3" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I5" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I6" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8729D20B-9EDA-4E99-827A-CDCDA414618E}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I3" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>773</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>250</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="I5" s="1">
+        <v>46162.041666666664</v>
       </c>
     </row>
   </sheetData>

--- a/documents/00. Database-ERD-Schemas.xlsx
+++ b/documents/00. Database-ERD-Schemas.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrosea-my.sharepoint.com/personal/harry_kurniansyah_petrosea_com/Documents/Documents/2_Harry_Kurniansyah_Docs/0_Very_Personal/MechSense/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BAF7C0-F6EF-40DF-9203-B60BC497B66A}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E75522D-1339-4755-B90B-ECED0186893A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ERD" sheetId="1" r:id="rId1"/>
-    <sheet name="Table - Site Master" sheetId="2" r:id="rId2"/>
-    <sheet name="Table - Brand Master" sheetId="3" r:id="rId3"/>
-    <sheet name="Table - Equipment Class Master" sheetId="4" r:id="rId4"/>
-    <sheet name="Table -Model Master" sheetId="5" r:id="rId5"/>
+    <sheet name="Table - Site Master" sheetId="2" r:id="rId1"/>
+    <sheet name="Table - Brand Master" sheetId="3" r:id="rId2"/>
+    <sheet name="Table - Equipment Class Master" sheetId="4" r:id="rId3"/>
+    <sheet name="Table - Model Master" sheetId="5" r:id="rId4"/>
+    <sheet name="Table - Equipment Master" sheetId="6" r:id="rId5"/>
+    <sheet name="Table - Hour Meter History" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="77">
   <si>
     <t>{uuid}</t>
   </si>
@@ -235,14 +236,75 @@
   <si>
     <t>brand_id
 (UUID)</t>
+  </si>
+  <si>
+    <t>site_id
+(UUID)</t>
+  </si>
+  <si>
+    <t>model_id
+(UUID)</t>
+  </si>
+  <si>
+    <t>serial_number
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>acquisition_date
+(DATE)</t>
+  </si>
+  <si>
+    <t>currency
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>acquisition_value
+(NUMERIC(10,2))</t>
+  </si>
+  <si>
+    <t>current_hm
+(NUMERIC(10,2))</t>
+  </si>
+  <si>
+    <t>unit_status
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>78WSOMETHING</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>unit_priority
+(BOOLEAN)</t>
+  </si>
+  <si>
+    <t>hour_meter
+(NUMERIC(10,2))</t>
+  </si>
+  <si>
+    <t>equipment_id
+(UUID)</t>
+  </si>
+  <si>
+    <t>submit_date
+(TIMESTAMP)</t>
+  </si>
+  <si>
+    <t>API_SYSTEM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -273,12 +335,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,15 +622,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C4114C-3269-42E0-A2EE-B55B0E7032E4}">
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -667,7 +722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F10698-B894-4157-9D90-FB68318B125C}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -826,7 +881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B34790-3214-40B1-A3B8-A15FC42E8D0D}">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1020,7 +1075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8729D20B-9EDA-4E99-827A-CDCDA414618E}">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1184,4 +1239,188 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA848FAC-5F88-4CC3-9D76-3095E418F625}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2">
+        <v>950000</v>
+      </c>
+      <c r="H2">
+        <v>1000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="N2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031EAB8B-E322-4254-9F67-BB8F132B9396}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2">
+        <v>1024</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46163</v>
+      </c>
+      <c r="E2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46163</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46163</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/documents/00. Database-ERD-Schemas.xlsx
+++ b/documents/00. Database-ERD-Schemas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrosea-my.sharepoint.com/personal/harry_kurniansyah_petrosea_com/Documents/Documents/2_Harry_Kurniansyah_Docs/0_Very_Personal/MechSense/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E75522D-1339-4755-B90B-ECED0186893A}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80B5E142-709F-4C5A-9F3A-3CEE52E79138}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table - Site Master" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="77">
   <si>
     <t>{uuid}</t>
   </si>
@@ -304,7 +304,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -335,14 +335,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1243,25 +1242,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA848FAC-5F88-4CC3-9D76-3095E418F625}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
@@ -1275,40 +1275,43 @@
         <v>63</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1321,34 +1324,34 @@
       <c r="D2" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="3">
         <v>45658</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>70</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>950000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1000</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>71</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="1">
-        <v>46162.041666666664</v>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>4</v>
       </c>
       <c r="N2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="O2" s="1">
         <v>46162.041666666664</v>
       </c>
     </row>

--- a/documents/00. Database-ERD-Schemas.xlsx
+++ b/documents/00. Database-ERD-Schemas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrosea-my.sharepoint.com/personal/harry_kurniansyah_petrosea_com/Documents/Documents/2_Harry_Kurniansyah_Docs/0_Very_Personal/MechSense/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80B5E142-709F-4C5A-9F3A-3CEE52E79138}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93A274FC-942C-461E-98DC-7D3C890B8EDB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table - Site Master" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Table - Model Master" sheetId="5" r:id="rId4"/>
     <sheet name="Table - Equipment Master" sheetId="6" r:id="rId5"/>
     <sheet name="Table - Hour Meter History" sheetId="7" r:id="rId6"/>
+    <sheet name="Table - Component Master" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1426,4 +1427,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56EE3AE-FFAB-472A-BB92-6D07A37EC867}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/documents/00. Database-ERD-Schemas.xlsx
+++ b/documents/00. Database-ERD-Schemas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrosea-my.sharepoint.com/personal/harry_kurniansyah_petrosea_com/Documents/Documents/2_Harry_Kurniansyah_Docs/0_Very_Personal/MechSense/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="383" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93A274FC-942C-461E-98DC-7D3C890B8EDB}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4149FFF4-3DDC-4D60-8AB6-6994953FC165}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table - Site Master" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Table - Equipment Master" sheetId="6" r:id="rId5"/>
     <sheet name="Table - Hour Meter History" sheetId="7" r:id="rId6"/>
     <sheet name="Table - Component Master" sheetId="8" r:id="rId7"/>
+    <sheet name="Table - Model Component Master" sheetId="9" r:id="rId8"/>
+    <sheet name="Table - Component Instance" sheetId="10" r:id="rId9"/>
+    <sheet name="Tabel - Equipment Status Log" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="89">
   <si>
     <t>{uuid}</t>
   </si>
@@ -297,6 +300,46 @@
   </si>
   <si>
     <t>API_SYSTEM</t>
+  </si>
+  <si>
+    <t>component_code
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>DT0123</t>
+  </si>
+  <si>
+    <t>component_name
+(VARCHAR)</t>
+  </si>
+  <si>
+    <t>component_master_id
+(UUID)</t>
+  </si>
+  <si>
+    <t>target_life_hm
+(UUID)</t>
+  </si>
+  <si>
+    <t>master_id</t>
+  </si>
+  <si>
+    <t>equipment_id</t>
+  </si>
+  <si>
+    <t>serial_number</t>
+  </si>
+  <si>
+    <t>installed_date</t>
+  </si>
+  <si>
+    <t>installed_equipment_hm</t>
+  </si>
+  <si>
+    <t>current_component_hm</t>
+  </si>
+  <si>
+    <t>status</t>
   </si>
 </sst>
 </file>
@@ -722,6 +765,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317A0D0E-7732-40F6-A8D3-3A3912AFC7BF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F10698-B894-4157-9D90-FB68318B125C}">
   <dimension ref="A1:H6"/>
@@ -1325,6 +1377,9 @@
       <c r="D2" t="s">
         <v>69</v>
       </c>
+      <c r="E2" t="s">
+        <v>78</v>
+      </c>
       <c r="F2" s="3">
         <v>45658</v>
       </c>
@@ -1431,9 +1486,167 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56EE3AE-FFAB-472A-BB92-6D07A37EC867}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="6" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D67D70-ED5C-422E-987D-DE89222C51A1}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46162.041666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59117C-1BF4-4906-ABC5-F2C7643F287C}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documents/00. Database-ERD-Schemas.xlsx
+++ b/documents/00. Database-ERD-Schemas.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrosea-my.sharepoint.com/personal/harry_kurniansyah_petrosea_com/Documents/Documents/2_Harry_Kurniansyah_Docs/0_Very_Personal/MechSense/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4149FFF4-3DDC-4D60-8AB6-6994953FC165}"/>
+  <xr:revisionPtr revIDLastSave="456" documentId="11_F25DC773A252ABDACC104813B1DE57565ADE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE491565-7F9A-4AAE-B649-5A6174320C09}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table - Site Master" sheetId="2" r:id="rId1"/>
@@ -24,10 +24,21 @@
     <sheet name="Table - Component Instance" sheetId="10" r:id="rId9"/>
     <sheet name="Tabel - Equipment Status Log" sheetId="11" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -666,6 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C4114C-3269-42E0-A2EE-B55B0E7032E4}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -767,6 +779,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317A0D0E-7732-40F6-A8D3-3A3912AFC7BF}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -776,6 +789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F10698-B894-4157-9D90-FB68318B125C}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -935,12 +949,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B34790-3214-40B1-A3B8-A15FC42E8D0D}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.109375" customWidth="1"/>
     <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
@@ -1129,6 +1144,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8729D20B-9EDA-4E99-827A-CDCDA414618E}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1295,6 +1311,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA848FAC-5F88-4CC3-9D76-3095E418F625}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1418,6 +1435,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031EAB8B-E322-4254-9F67-BB8F132B9396}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1486,6 +1504,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56EE3AE-FFAB-472A-BB92-6D07A37EC867}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1545,6 +1564,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D67D70-ED5C-422E-987D-DE89222C51A1}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1602,6 +1622,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A59117C-1BF4-4906-ABC5-F2C7643F287C}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
